--- a/public/templates/office/Phase0_입찰타당성_Go_NoGo_심의표.xlsx
+++ b/public/templates/office/Phase0_입찰타당성_Go_NoGo_심의표.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Go_NoGo_심의표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Go_NoGo_심의평가표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_리스크_완화계획" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,12 +31,13 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="0064748B"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -44,11 +48,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00334155"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001E293B"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +67,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,28 +117,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,30 +546,29 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Go_NoGo_심의표</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>[EMP-XLS-P0-02] 입찰 타당성 사전 심의표 (Go / No-Go Decision Matrix) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>엠파시 사업 및 개발 방법론 표준 시트 (주식회사 엠파시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
+          <t>한빛글로벌 SyncGuard AI 구축 사업 수주 타당성·수익성·기술적합성 7대 영역 정량 평가 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>번호</t>
@@ -523,7 +581,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>핵심 점검 질문 및 위험 요인</t>
+          <t>핵심 점검 항목 (SyncGuard AI 기준)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -543,16 +601,16 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>환산 점수</t>
+          <t>환산점수</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>검토 의견</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+          <t>검토 의견 및 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -561,130 +619,130 @@
           <t>기술 적합성</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>당사 코어 솔루션(SyncSeries/Verse) 및 기술 스택과 80% 이상 부합 여부</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>당사 SyncSeries/AI 코어 엔진 및 하이브리드 RAG 아키텍처 부합도</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="E5" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="8">
         <f>E5*F5/10</f>
         <v/>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>당사 코어 아키텍처와 95% 일치</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>3단계 LLM 파이프라인 및 pgvector 아키텍처 95% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>인프라 및 환경</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>온프레미스 망분리, GPU 인프라, 클라우드 사양 호환성 보장 여부</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>인프라·보안 호환성</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>한빛글로벌 AWS EKS 망분리(내부/대외 ALB) 및 SSO 연동 호환성</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="13">
         <f>E6*F6/10</f>
         <v/>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>망분리 vLLM 폐쇄망 구성 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>기존 한빛글로벌 표준 EKS 아키텍처 가이드 완벽 부합</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>데이터 접근성</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>AI 파인튜닝/RAG용 원천 데이터 품질, 보안성, 제공 시점 보장 여부</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
+          <t>도메인 데이터 확보</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>ProductLab 전성분 뷰, 식약처 고시 및 100대 심의 룰셋 확보 가능성</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4" t="n">
+      <c r="E7" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F7" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="8">
         <f>E7*F7/10</f>
         <v/>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Sprint 1 데이터 샘플 이관 합의</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>착수 즉시 골든셋 50문항 및 전성분 읽기전용 뷰 제공 합의</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>일정 타당성</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>과업 범위 대비 납기의 물리적 실현 가능성 및 단축 리스크 유무</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>납기 타당성</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>6개월(2026.05~10) 내 분석·설계·구현·2주 시범운영 완수 가능성</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="13">
         <f>E8*F8/10</f>
         <v/>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>스프린트 2주 단위 공정 타이트</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>기간계 어댑터 전문 협력사(㈜데이터브릿지) 분담으로 일정 충분</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
@@ -693,136 +751,304 @@
           <t>원가 및 수익성</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>예정가 대비 목표 영업이익률 25% 확보 및 직접 원가 비율 적정성</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>총 예정가 4.5억 원 대비 목표 공헌이익률 28% 이상 확보 여부</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="8">
         <f>E9*F9/10</f>
         <v/>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>예상 영업이익률 28.4% 확보</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>직접원가 3.18억 원, 예상 영업이익률 29.3% 달성 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>수행 조직 가용성</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>즉시 투입 가능한 핵심 PM, 아키텍트, 시니어 개발자 확보 여부</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>핵심 인력 가용성</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>특급 PM(박진우), AI 아키텍트(강동현) 등 본사 정규직 전담 배치</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="13">
         <f>E10*F10/10</f>
         <v/>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>정규직 전담팀 100% 가용</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>핵심 리더 5명 100% 즉시 투입 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>보안 및 규제 제약</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>금융감독원 망분리, 시큐어코딩 49개, 지체상금 조항 적정성</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
+          <t>계약·법무 리스크</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>지체상금(0.075%), LLM API 실비 분리, 지식재산권 공동소유 조건</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="8">
         <f>E11*F11/10</f>
         <v/>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>지체상금 1일 0.075% 표준 준수</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>독소조항 없음, AI 토큰 비용 발주처 실비 부담 명문화</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>총점 합산</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>종합 판정 기준: 70점 이상 Go / 60~69점 조건부 / 60점 미만 포기</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>종합 판정</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>판정 기준: 80점 이상 적극 수주(Go) / 70~79점 조건부 / 70점 미만 포기</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="17">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="17">
         <f>SUM(G5:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>최종 판정: Go (수주 추진)</t>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>최종 판정: 89.3점 — 적극 입찰 참여 (Go 확정)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[EMP-XLS-P0-02] 입찰 타당성 사전 심의표 (Go / No-Go Decision Matrix) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>한빛글로벌 SyncGuard AI 구축 사업 수주 타당성·수익성·기술적합성 7대 영역 정량 평가 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>리스크 ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>식별된 입찰·수행 리스크</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>영향도</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>발생확률</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>사전 완화 대책 (제안서 및 계약 특약 반영사항)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>담당 임원</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>RSK-01</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>디자인 폰트·배경 합성 이미지의 OCR 오인식 가능성</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Upstage Document Parse + Clova OCR 듀얼 검증 및 UI 인라인 보정 에디터 제공</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>강동현 수석</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>RSK-02</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>운영 중 LLM API 토큰 호출량 급증에 따른 비용 분쟁</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>용역계약서 제3조에 LLM/OCR API 호출비 발주처 실비 부담 명시 및 Redis 캐시 적용</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>박진우 수석</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>RSK-03</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>대외 방화벽 보안 심의 대기(평균 5~7일)로 인한 연동 지연</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>상세설계 초기에 방화벽 신청서(EMP_DEG_091) 조기 제출 및 Mock 서버 선행 개발</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>강동현 수석</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/templates/office/Phase0_입찰타당성_Go_NoGo_심의표.xlsx
+++ b/public/templates/office/Phase0_입찰타당성_Go_NoGo_심의표.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Go_NoGo_심의평가표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Go_NoGo_검증평가표" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_리스크_완화계획" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -557,14 +557,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[EMP-XLS-P0-02] 입찰 타당성 사전 심의표 (Go / No-Go Decision Matrix) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[EMP-XLS-P0-02] 입찰 타당성 사전 검증표 (Go / No-Go Decision Matrix) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 구축 사업 수주 타당성·수익성·기술적합성 7대 영역 정량 평가 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+          <t>한빛글로벌 SyncFlow AI 구축 사업 수주 타당성·수익성·기술적합성 7대 영역 정량 평가 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>핵심 점검 항목 (SyncGuard AI 기준)</t>
+          <t>핵심 점검 항목 (SyncFlow AI 기준)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>ProductLab 전성분 뷰, 식약처 고시 및 100대 심의 룰셋 확보 가능성</t>
+          <t>PLM-Nexus 자재BOM 뷰, 공정위·표준원 고시 및 100대 검증 룰셋 확보 가능성</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>착수 즉시 골든셋 50문항 및 전성분 읽기전용 뷰 제공 합의</t>
+          <t>착수 즉시 골든셋 50문항 및 자재BOM 읽기전용 뷰 제공 합의</t>
         </is>
       </c>
     </row>
@@ -906,14 +906,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[EMP-XLS-P0-02] 입찰 타당성 사전 심의표 (Go / No-Go Decision Matrix) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[EMP-XLS-P0-02] 입찰 타당성 사전 검증표 (Go / No-Go Decision Matrix) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 구축 사업 수주 타당성·수익성·기술적합성 7대 영역 정량 평가 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+          <t>한빛글로벌 SyncFlow AI 구축 사업 수주 타당성·수익성·기술적합성 7대 영역 정량 평가 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Upstage Document Parse + Clova OCR 듀얼 검증 및 UI 인라인 보정 에디터 제공</t>
+          <t>EnterpriseVision Document Parse + Enterprise Vision OCR 듀얼 검증 및 UI 인라인 보정 에디터 제공</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>대외 방화벽 보안 심의 대기(평균 5~7일)로 인한 연동 지연</t>
+          <t>대외 방화벽 보안 검토 대기(평균 5~7일)로 인한 연동 지연</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
